--- a/eva_workspace/sigmaV/report/analysis.xlsx
+++ b/eva_workspace/sigmaV/report/analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\user\Desktop\ICDLab\ICDLAB_Final_Project\eva_workspace\sigmaV\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A5514FD-5F0F-4F6C-B235-25DCE429DD23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98B677A8-11A0-4766-B799-C6FF14E6E183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7680" yWindow="3300" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2544" yWindow="5076" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -369,15 +369,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -396,11 +396,8 @@
       <c r="F2">
         <v>30</v>
       </c>
-      <c r="G2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -419,62 +416,53 @@
       <c r="F3">
         <v>3957</v>
       </c>
-      <c r="G3">
-        <v>6630</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="C4">
-        <v>563</v>
+        <v>583</v>
       </c>
       <c r="D4">
-        <v>1051</v>
+        <v>1071</v>
       </c>
       <c r="E4">
-        <v>2385</v>
+        <v>2405</v>
       </c>
       <c r="F4">
-        <v>3729</v>
-      </c>
-      <c r="G4">
-        <v>6365</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>3749</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
       <c r="B5">
-        <v>88</v>
+        <v>138</v>
       </c>
       <c r="C5">
-        <v>381</v>
+        <v>566</v>
       </c>
       <c r="D5">
-        <v>728</v>
+        <v>1023</v>
       </c>
       <c r="E5">
-        <v>1631</v>
+        <v>2281</v>
       </c>
       <c r="F5">
-        <v>2503</v>
-      </c>
-      <c r="G5">
-        <v>4215</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>3478</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>0</v>
       </c>
@@ -493,11 +481,8 @@
       <c r="F8">
         <v>30</v>
       </c>
-      <c r="G8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -516,62 +501,53 @@
       <c r="F9">
         <v>8369</v>
       </c>
-      <c r="G9">
-        <v>13985</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>5</v>
       </c>
       <c r="B10">
-        <v>135</v>
+        <v>240</v>
       </c>
       <c r="C10">
-        <v>1032</v>
+        <v>1137</v>
       </c>
       <c r="D10">
-        <v>1951</v>
+        <v>2056</v>
       </c>
       <c r="E10">
-        <v>4537</v>
+        <v>4642</v>
       </c>
       <c r="F10">
-        <v>7307</v>
-      </c>
-      <c r="G10">
-        <v>12758</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+        <v>7412</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>6</v>
       </c>
       <c r="B11">
-        <v>105</v>
+        <v>240</v>
       </c>
       <c r="C11">
-        <v>456</v>
+        <v>1016</v>
       </c>
       <c r="D11">
-        <v>841</v>
+        <v>1701</v>
       </c>
       <c r="E11">
-        <v>1871</v>
+        <v>3721</v>
       </c>
       <c r="F11">
-        <v>2864</v>
-      </c>
-      <c r="G11">
-        <v>4819</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+        <v>5644</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -590,11 +566,8 @@
       <c r="F14">
         <v>30</v>
       </c>
-      <c r="G14">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -613,62 +586,53 @@
       <c r="F15">
         <v>17214</v>
       </c>
-      <c r="G15">
-        <v>28754</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>5</v>
       </c>
       <c r="B16">
-        <v>188</v>
+        <v>558</v>
       </c>
       <c r="C16">
-        <v>1869</v>
+        <v>2239</v>
       </c>
       <c r="D16">
-        <v>3641</v>
+        <v>4011</v>
       </c>
       <c r="E16">
-        <v>8733</v>
+        <v>9103</v>
       </c>
       <c r="F16">
-        <v>14101</v>
-      </c>
-      <c r="G16">
-        <v>24873</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+        <v>14471</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>6</v>
       </c>
       <c r="B17">
-        <v>158</v>
+        <v>558</v>
       </c>
       <c r="C17">
-        <v>600</v>
+        <v>1880</v>
       </c>
       <c r="D17">
-        <v>1058</v>
+        <v>3003</v>
       </c>
       <c r="E17">
-        <v>2341</v>
+        <v>6541</v>
       </c>
       <c r="F17">
-        <v>3590</v>
-      </c>
-      <c r="G17">
-        <v>5994</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>0</v>
       </c>
@@ -687,11 +651,8 @@
       <c r="F20">
         <v>30</v>
       </c>
-      <c r="G20">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -710,54 +671,45 @@
       <c r="F21">
         <v>34554</v>
       </c>
-      <c r="G21">
-        <v>57542</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>5</v>
       </c>
       <c r="B22">
-        <v>300</v>
+        <v>1230</v>
       </c>
       <c r="C22">
-        <v>3626</v>
+        <v>4556</v>
       </c>
       <c r="D22">
-        <v>7101</v>
+        <v>8031</v>
       </c>
       <c r="E22">
-        <v>17279</v>
+        <v>18209</v>
       </c>
       <c r="F22">
-        <v>28176</v>
-      </c>
-      <c r="G22">
-        <v>49481</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+        <v>29106</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>6</v>
       </c>
       <c r="B23">
-        <v>270</v>
+        <v>1230</v>
       </c>
       <c r="C23">
-        <v>908</v>
+        <v>3728</v>
       </c>
       <c r="D23">
-        <v>1500</v>
+        <v>5655</v>
       </c>
       <c r="E23">
-        <v>3280</v>
+        <v>12175</v>
       </c>
       <c r="F23">
-        <v>5023</v>
-      </c>
-      <c r="G23">
-        <v>8275</v>
+        <v>18598</v>
       </c>
     </row>
   </sheetData>
